--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_251_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_251_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>4</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
         <v>6</v>
@@ -1727,16 +1727,16 @@
         <v>22</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
         <v>6</v>
@@ -2315,7 +2315,7 @@
         <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>2</v>
@@ -3102,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>10</v>
@@ -3491,16 +3491,16 @@
         <v>26</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>8</v>
@@ -3827,16 +3827,16 @@
         <v>138</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X30" t="n">
         <v>39</v>
@@ -4488,7 +4488,7 @@
         <v>6</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4880,16 +4880,16 @@
         <v>30</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>5</v>
@@ -5468,16 +5468,16 @@
         <v>11</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>5</v>
@@ -5664,7 +5664,7 @@
         <v>5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6252,10 +6252,10 @@
         <v>14</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>108</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
         <v>24</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_251_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_251_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -692,20 +692,20 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>82.98</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="P3" t="n">
         <v>7</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>68.57</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1543,14 +1543,14 @@
         <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1772,25 +1772,25 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -2523,14 +2523,14 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -3111,14 +3111,14 @@
         <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3503,10 +3503,10 @@
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>12</v>
       </c>
       <c r="X30" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="Y30" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4892,14 +4892,14 @@
         <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5480,14 +5480,14 @@
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6796,14 +6796,14 @@
         <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Y48" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
